--- a/data/passengers.xlsx
+++ b/data/passengers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git Workspace\chaitya-paripati-2026-\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0C23890-60BC-4B30-861C-E0232E32687D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05591766-D31F-4024-9506-8FD510BF3579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{6314CF59-B62F-4ABE-803E-B3252DC11DF7}"/>
   </bookViews>
@@ -3813,7 +3813,7 @@
         <v>73</v>
       </c>
       <c r="C71" s="2">
-        <v>1234567890</v>
+        <v>7709506569</v>
       </c>
       <c r="D71" s="4">
         <v>33</v>

--- a/data/passengers.xlsx
+++ b/data/passengers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git Workspace\chaitya-paripati-2026-\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05591766-D31F-4024-9506-8FD510BF3579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B08EB098-B30E-4E92-B6E3-805B22929633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{6314CF59-B62F-4ABE-803E-B3252DC11DF7}"/>
   </bookViews>
@@ -1083,7 +1083,7 @@
         <v>8</v>
       </c>
       <c r="C6" s="2">
-        <v>1234567890</v>
+        <v>9028389767</v>
       </c>
       <c r="D6" s="4">
         <v>25</v>
@@ -1671,7 +1671,7 @@
         <v>22</v>
       </c>
       <c r="C20" s="2">
-        <v>1234567890</v>
+        <v>7666786214</v>
       </c>
       <c r="D20" s="4">
         <v>40</v>

--- a/data/passengers.xlsx
+++ b/data/passengers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git Workspace\chaitya-paripati-2026-\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B08EB098-B30E-4E92-B6E3-805B22929633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90ABEABC-9C37-4DAE-B184-A462201B692D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{6314CF59-B62F-4ABE-803E-B3252DC11DF7}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="126">
   <si>
     <t>Name</t>
   </si>
@@ -42,9 +42,6 @@
     <t>Mobile</t>
   </si>
   <si>
-    <t>Train</t>
-  </si>
-  <si>
     <t>Coach</t>
   </si>
   <si>
@@ -381,9 +378,6 @@
     <t>Birth</t>
   </si>
   <si>
-    <t>Return Train</t>
-  </si>
-  <si>
     <t>Return Coach</t>
   </si>
   <si>
@@ -391,6 +385,33 @@
   </si>
   <si>
     <t>Return Birth</t>
+  </si>
+  <si>
+    <t>Surat to Pune (Date)</t>
+  </si>
+  <si>
+    <t>Pune to Surat</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Daund Express</t>
+  </si>
+  <si>
+    <t>TrainNameR</t>
+  </si>
+  <si>
+    <t>DateR</t>
+  </si>
+  <si>
+    <t>TrainName</t>
+  </si>
+  <si>
+    <t>TrainNo</t>
+  </si>
+  <si>
+    <t>TrainNoR</t>
   </si>
 </sst>
 </file>
@@ -489,7 +510,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -532,6 +553,18 @@
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -848,7 +881,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5512A41-4850-49E1-B3B4-F7316635A4D6}">
-  <dimension ref="A1:M91"/>
+  <dimension ref="A1:S91"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="3.9296875" bestFit="1" customWidth="1"/>
@@ -857,18 +890,22 @@
     <col min="4" max="4" width="3.73046875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="3.3984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="4.73046875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.46484375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.1328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.53125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.9296875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.9296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.9296875" customWidth="1"/>
+    <col min="9" max="9" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.46484375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.1328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.59765625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.53125" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="10.53125" customWidth="1"/>
+    <col min="17" max="17" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.9296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -877,42 +914,60 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E1" t="s">
         <v>111</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>118</v>
+      </c>
+      <c r="G1" t="s">
+        <v>119</v>
+      </c>
+      <c r="H1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" t="s">
         <v>112</v>
       </c>
-      <c r="F1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>113</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" t="s">
+        <v>117</v>
+      </c>
+      <c r="N1" t="s">
+        <v>122</v>
+      </c>
+      <c r="O1" t="s">
+        <v>125</v>
+      </c>
+      <c r="P1" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q1" t="s">
         <v>114</v>
       </c>
-      <c r="J1" t="s">
+      <c r="R1" t="s">
         <v>115</v>
       </c>
-      <c r="K1" t="s">
+      <c r="S1" t="s">
         <v>116</v>
       </c>
-      <c r="L1" t="s">
-        <v>117</v>
-      </c>
-      <c r="M1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+    </row>
+    <row r="2" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="2">
         <v>1234567890</v>
@@ -921,40 +976,58 @@
         <v>86</v>
       </c>
       <c r="E2" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F2" s="4">
+        <v>1234</v>
+      </c>
+      <c r="G2" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H2" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J2" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="F2" s="4">
-        <v>1234</v>
-      </c>
-      <c r="G2" s="5" t="s">
+      <c r="K2" s="5">
+        <v>71</v>
+      </c>
+      <c r="L2" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="H2" s="5">
-        <v>71</v>
-      </c>
-      <c r="I2" s="6" t="s">
+      <c r="M2" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N2" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O2" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="R2" s="7">
+        <v>12</v>
+      </c>
+      <c r="S2" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="J2" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L2" s="7">
-        <v>12</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+    </row>
+    <row r="3" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <f>A2+1</f>
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" s="2">
         <v>1234567890</v>
@@ -963,40 +1036,58 @@
         <v>78</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F3" s="4">
+        <v>1234</v>
+      </c>
+      <c r="G3" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H3" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="K3" s="5">
+        <v>66</v>
+      </c>
+      <c r="L3" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="F3" s="4">
-        <v>1234</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="H3" s="5">
-        <v>66</v>
-      </c>
-      <c r="I3" s="6" t="s">
+      <c r="M3" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N3" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O3" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="R3" s="7">
+        <v>11</v>
+      </c>
+      <c r="S3" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="J3" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L3" s="7">
-        <v>11</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="2">
         <v>1234567890</v>
@@ -1005,40 +1096,58 @@
         <v>27</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F4" s="4">
+        <v>1234</v>
+      </c>
+      <c r="G4" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H4" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J4" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="4">
-        <v>1234</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="H4" s="5">
+      <c r="K4" s="5">
         <v>67</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="L4" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="M4" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N4" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O4" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q4" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="J4" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="R4" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="2">
         <v>1234567890</v>
@@ -1047,40 +1156,58 @@
         <v>27</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F5" s="4">
+        <v>1234</v>
+      </c>
+      <c r="G5" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H5" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="K5" s="5">
+        <v>69</v>
+      </c>
+      <c r="L5" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="F5" s="4">
-        <v>1234</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="H5" s="5">
-        <v>69</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="J5" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="M5" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N5" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O5" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2">
         <v>9028389767</v>
@@ -1089,40 +1216,58 @@
         <v>25</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F6" s="4">
+        <v>1234</v>
+      </c>
+      <c r="G6" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H6" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J6" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="F6" s="4">
-        <v>1234</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="H6" s="5">
+      <c r="K6" s="5">
         <v>70</v>
       </c>
-      <c r="I6" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="J6" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L6" s="7">
+      <c r="L6" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="M6" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N6" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O6" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q6" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="R6" s="7">
         <v>13</v>
       </c>
-      <c r="M6" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S6" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7" s="2">
         <v>1234567890</v>
@@ -1131,40 +1276,58 @@
         <v>43</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F7" s="4">
         <v>1234</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="H7" s="5">
+      <c r="G7" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H7" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="K7" s="5">
         <v>72</v>
       </c>
-      <c r="I7" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="J7" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L7" s="7">
+      <c r="L7" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="M7" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N7" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O7" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q7" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="R7" s="7">
         <v>14</v>
       </c>
-      <c r="M7" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S7" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" s="2">
         <v>1234567890</v>
@@ -1173,40 +1336,58 @@
         <v>46</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F8" s="4">
         <v>1234</v>
       </c>
-      <c r="G8" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="H8" s="8">
+      <c r="G8" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H8" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="K8" s="8">
         <v>25</v>
       </c>
-      <c r="I8" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="J8" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L8" s="7">
+      <c r="L8" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="M8" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N8" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O8" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q8" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="R8" s="7">
         <v>16</v>
       </c>
-      <c r="M8" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S8" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9" s="2">
         <v>1234567890</v>
@@ -1215,40 +1396,58 @@
         <v>53</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F9" s="4">
         <v>1234</v>
       </c>
-      <c r="G9" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="H9" s="8">
+      <c r="G9" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H9" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="K9" s="8">
         <v>27</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="L9" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="M9" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N9" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O9" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P9" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q9" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="J9" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="R9" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="S9" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10" s="2">
         <v>1234567890</v>
@@ -1257,40 +1456,58 @@
         <v>50</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F10" s="4">
         <v>1234</v>
       </c>
-      <c r="G10" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="H10" s="8">
+      <c r="G10" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H10" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="K10" s="8">
         <v>28</v>
       </c>
-      <c r="I10" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="J10" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>104</v>
-      </c>
       <c r="L10" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+        <v>99</v>
+      </c>
+      <c r="M10" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N10" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O10" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P10" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q10" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="R10" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="S10" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="2">
         <v>1234567890</v>
@@ -1299,40 +1516,58 @@
         <v>24</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F11" s="4">
         <v>1234</v>
       </c>
-      <c r="G11" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="H11" s="8">
+      <c r="G11" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H11" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="K11" s="8">
         <v>29</v>
       </c>
-      <c r="I11" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="J11" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>104</v>
-      </c>
       <c r="L11" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+        <v>101</v>
+      </c>
+      <c r="M11" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N11" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O11" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P11" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q11" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="R11" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="S11" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" s="2">
         <v>1234567890</v>
@@ -1341,40 +1576,58 @@
         <v>82</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F12" s="4">
         <v>1234</v>
       </c>
-      <c r="G12" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="H12" s="8">
+      <c r="G12" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H12" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="K12" s="8">
         <v>26</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="J12" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L12" s="7">
+      <c r="L12" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="M12" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N12" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O12" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P12" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q12" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="R12" s="7">
         <v>15</v>
       </c>
-      <c r="M12" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S12" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C13" s="2">
         <v>1234567890</v>
@@ -1383,40 +1636,58 @@
         <v>58</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F13" s="4">
         <v>1234</v>
       </c>
-      <c r="G13" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="H13" s="8">
+      <c r="G13" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H13" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="K13" s="8">
         <v>30</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="J13" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K13" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="L13" s="8">
+      <c r="L13" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="M13" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N13" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O13" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P13" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q13" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="R13" s="8">
         <v>42</v>
       </c>
-      <c r="M13" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S13" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14" s="2">
         <v>1234567890</v>
@@ -1425,40 +1696,58 @@
         <v>54</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F14" s="4">
         <v>1234</v>
       </c>
-      <c r="G14" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H14" s="7">
+      <c r="G14" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H14" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K14" s="7">
         <v>49</v>
       </c>
-      <c r="I14" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="J14" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K14" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="L14" s="9">
+      <c r="L14" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="M14" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N14" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O14" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P14" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q14" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="R14" s="9">
         <v>1</v>
       </c>
-      <c r="M14" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S14" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C15" s="2">
         <v>1234567890</v>
@@ -1467,40 +1756,58 @@
         <v>27</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F15" s="4">
         <v>1234</v>
       </c>
-      <c r="G15" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H15" s="7">
+      <c r="G15" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H15" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K15" s="7">
         <v>50</v>
       </c>
-      <c r="I15" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="J15" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K15" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="L15" s="9">
+      <c r="L15" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="M15" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N15" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O15" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P15" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q15" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="R15" s="9">
         <v>2</v>
       </c>
-      <c r="M15" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S15" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C16" s="2">
         <v>1234567890</v>
@@ -1509,40 +1816,58 @@
         <v>30</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F16" s="4">
         <v>1234</v>
       </c>
-      <c r="G16" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H16" s="7">
+      <c r="G16" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H16" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K16" s="7">
         <v>51</v>
       </c>
-      <c r="I16" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="J16" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K16" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="L16" s="9">
+      <c r="L16" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="M16" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N16" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O16" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P16" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q16" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="R16" s="9">
         <v>3</v>
       </c>
-      <c r="M16" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S16" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C17" s="2">
         <v>1234567890</v>
@@ -1551,40 +1876,58 @@
         <v>28</v>
       </c>
       <c r="E17" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F17" s="4">
+        <v>1234</v>
+      </c>
+      <c r="G17" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H17" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K17" s="7">
+        <v>53</v>
+      </c>
+      <c r="L17" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F17" s="4">
-        <v>1234</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H17" s="7">
-        <v>53</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="J17" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K17" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="L17" s="9">
+      <c r="M17" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N17" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O17" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P17" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q17" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="R17" s="9">
         <v>5</v>
       </c>
-      <c r="M17" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S17" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C18" s="2">
         <v>1234567890</v>
@@ -1593,40 +1936,58 @@
         <v>56</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F18" s="4">
         <v>1234</v>
       </c>
-      <c r="G18" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H18" s="7">
+      <c r="G18" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H18" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K18" s="7">
         <v>54</v>
       </c>
-      <c r="I18" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="J18" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K18" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="L18" s="9">
+      <c r="L18" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="M18" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N18" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O18" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P18" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q18" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="R18" s="9">
         <v>6</v>
       </c>
-      <c r="M18" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S18" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C19" s="2">
         <v>1234567890</v>
@@ -1635,40 +1996,58 @@
         <v>50</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F19" s="4">
         <v>1234</v>
       </c>
-      <c r="G19" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H19" s="7">
+      <c r="G19" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H19" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K19" s="7">
         <v>56</v>
       </c>
-      <c r="I19" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="J19" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K19" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="L19" s="9">
+      <c r="L19" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="M19" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N19" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O19" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P19" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q19" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="R19" s="9">
         <v>4</v>
       </c>
-      <c r="M19" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S19" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C20" s="2">
         <v>7666786214</v>
@@ -1677,40 +2056,58 @@
         <v>40</v>
       </c>
       <c r="E20" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F20" s="4">
+        <v>1234</v>
+      </c>
+      <c r="G20" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H20" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J20" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="F20" s="4">
-        <v>1234</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="H20" s="10">
+      <c r="K20" s="10">
         <v>58</v>
       </c>
-      <c r="I20" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="J20" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K20" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="L20" s="11">
+      <c r="L20" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="M20" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N20" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O20" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P20" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q20" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="R20" s="11">
         <v>42</v>
       </c>
-      <c r="M20" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S20" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C21" s="2">
         <v>1234567890</v>
@@ -1719,40 +2116,58 @@
         <v>38</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F21" s="4">
         <v>1234</v>
       </c>
-      <c r="G21" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="H21" s="10">
+      <c r="G21" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H21" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J21" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="K21" s="10">
         <v>59</v>
       </c>
-      <c r="I21" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="J21" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K21" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="L21" s="11">
+      <c r="L21" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="M21" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N21" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O21" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P21" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q21" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="R21" s="11">
         <v>43</v>
       </c>
-      <c r="M21" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S21" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C22" s="2">
         <v>1234567890</v>
@@ -1761,40 +2176,58 @@
         <v>13</v>
       </c>
       <c r="E22" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F22" s="4">
+        <v>1234</v>
+      </c>
+      <c r="G22" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H22" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="K22" s="10">
+        <v>61</v>
+      </c>
+      <c r="L22" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F22" s="4">
-        <v>1234</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="H22" s="10">
-        <v>61</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="J22" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K22" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="L22" s="11">
+      <c r="M22" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N22" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O22" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P22" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q22" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="R22" s="11">
         <v>44</v>
       </c>
-      <c r="M22" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S22" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C23" s="2">
         <v>1234567890</v>
@@ -1803,40 +2236,58 @@
         <v>23</v>
       </c>
       <c r="E23" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F23" s="4">
+        <v>1234</v>
+      </c>
+      <c r="G23" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H23" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="K23" s="10">
+        <v>62</v>
+      </c>
+      <c r="L23" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="M23" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N23" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O23" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P23" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q23" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="R23" s="11">
+        <v>45</v>
+      </c>
+      <c r="S23" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F23" s="4">
-        <v>1234</v>
-      </c>
-      <c r="G23" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="H23" s="10">
-        <v>62</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="J23" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K23" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="L23" s="11">
-        <v>45</v>
-      </c>
-      <c r="M23" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+    </row>
+    <row r="24" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C24" s="2">
         <v>1234567890</v>
@@ -1845,40 +2296,58 @@
         <v>56</v>
       </c>
       <c r="E24" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F24" s="4">
+        <v>1234</v>
+      </c>
+      <c r="G24" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H24" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J24" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="F24" s="4">
-        <v>1234</v>
-      </c>
-      <c r="G24" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="H24" s="10">
+      <c r="K24" s="10">
         <v>64</v>
       </c>
-      <c r="I24" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="J24" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K24" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="L24" s="11">
+      <c r="L24" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="M24" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N24" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O24" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P24" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q24" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="R24" s="11">
         <v>46</v>
       </c>
-      <c r="M24" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S24" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A25" s="1">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C25" s="2">
         <v>1234567890</v>
@@ -1887,40 +2356,58 @@
         <v>52</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F25" s="4">
         <v>1234</v>
       </c>
-      <c r="G25" s="10" t="s">
+      <c r="G25" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H25" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="K25" s="10">
+        <v>63</v>
+      </c>
+      <c r="L25" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="H25" s="10">
-        <v>63</v>
-      </c>
-      <c r="I25" s="4" t="s">
+      <c r="M25" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N25" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O25" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P25" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q25" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="R25" s="11">
+        <v>41</v>
+      </c>
+      <c r="S25" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="J25" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K25" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="L25" s="11">
-        <v>41</v>
-      </c>
-      <c r="M25" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+    </row>
+    <row r="26" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C26" s="2">
         <v>1234567890</v>
@@ -1929,40 +2416,58 @@
         <v>55</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F26" s="4">
         <v>1234</v>
       </c>
-      <c r="G26" s="13" t="s">
+      <c r="G26" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H26" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J26" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="K26" s="13">
+        <v>50</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="M26" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N26" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O26" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P26" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q26" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="H26" s="13">
-        <v>50</v>
-      </c>
-      <c r="I26" s="6" t="s">
+      <c r="R26" s="13">
+        <v>19</v>
+      </c>
+      <c r="S26" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="J26" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K26" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="L26" s="13">
-        <v>19</v>
-      </c>
-      <c r="M26" s="6" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+    </row>
+    <row r="27" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A27" s="1">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C27" s="2">
         <v>1234567890</v>
@@ -1971,40 +2476,58 @@
         <v>53</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F27" s="4">
         <v>1234</v>
       </c>
-      <c r="G27" s="13" t="s">
+      <c r="G27" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H27" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J27" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="K27" s="13">
+        <v>49</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="M27" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N27" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O27" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P27" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q27" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="H27" s="13">
-        <v>49</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="J27" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K27" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="L27" s="13">
+      <c r="R27" s="13">
         <v>17</v>
       </c>
-      <c r="M27" s="6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S27" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A28" s="1">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C28" s="2">
         <v>1234567890</v>
@@ -2013,40 +2536,58 @@
         <v>64</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F28" s="4">
         <v>1234</v>
       </c>
-      <c r="G28" s="13" t="s">
+      <c r="G28" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H28" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J28" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="K28" s="13">
+        <v>51</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="M28" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N28" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O28" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P28" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q28" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="H28" s="13">
-        <v>51</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="J28" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K28" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="L28" s="13">
+      <c r="R28" s="13">
         <v>20</v>
       </c>
-      <c r="M28" s="6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S28" s="6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A29" s="1">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C29" s="2">
         <v>1234567890</v>
@@ -2055,40 +2596,58 @@
         <v>45</v>
       </c>
       <c r="E29" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F29" s="4">
+        <v>1234</v>
+      </c>
+      <c r="G29" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H29" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J29" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="K29" s="13">
+        <v>53</v>
+      </c>
+      <c r="L29" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="F29" s="4">
-        <v>1234</v>
-      </c>
-      <c r="G29" s="13" t="s">
+      <c r="M29" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N29" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O29" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P29" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q29" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="H29" s="13">
-        <v>53</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="J29" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K29" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="L29" s="13">
+      <c r="R29" s="13">
         <v>18</v>
       </c>
-      <c r="M29" s="6" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S29" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A30" s="1">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C30" s="2">
         <v>1234567890</v>
@@ -2097,40 +2656,58 @@
         <v>47</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F30" s="4">
         <v>1234</v>
       </c>
-      <c r="G30" s="13" t="s">
+      <c r="G30" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H30" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J30" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="K30" s="13">
+        <v>54</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="M30" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N30" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O30" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P30" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q30" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="H30" s="13">
-        <v>54</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="J30" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K30" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="L30" s="13">
+      <c r="R30" s="13">
         <v>22</v>
       </c>
-      <c r="M30" s="6" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S30" s="6" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A31" s="1">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C31" s="2">
         <v>1234567890</v>
@@ -2139,40 +2716,58 @@
         <v>29</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F31" s="4">
         <v>1234</v>
       </c>
-      <c r="G31" s="13" t="s">
+      <c r="G31" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H31" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J31" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="K31" s="13">
+        <v>56</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="M31" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N31" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O31" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P31" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q31" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="H31" s="13">
-        <v>56</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="J31" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="L31" s="13">
+      <c r="R31" s="13">
         <v>21</v>
       </c>
-      <c r="M31" s="6" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S31" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C32" s="2">
         <v>1234567890</v>
@@ -2181,40 +2776,58 @@
         <v>26</v>
       </c>
       <c r="E32" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F32" s="4">
+        <v>1234</v>
+      </c>
+      <c r="G32" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H32" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K32" s="7">
+        <v>58</v>
+      </c>
+      <c r="L32" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F32" s="4">
-        <v>1234</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H32" s="7">
-        <v>58</v>
-      </c>
-      <c r="I32" s="4" t="s">
+      <c r="M32" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N32" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O32" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P32" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q32" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="R32" s="9">
+        <v>43</v>
+      </c>
+      <c r="S32" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="J32" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K32" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="L32" s="9">
-        <v>43</v>
-      </c>
-      <c r="M32" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+    </row>
+    <row r="33" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C33" s="2">
         <v>1234567890</v>
@@ -2223,40 +2836,58 @@
         <v>72</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F33" s="4">
         <v>1234</v>
       </c>
-      <c r="G33" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H33" s="7">
+      <c r="G33" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H33" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K33" s="7">
         <v>59</v>
       </c>
-      <c r="I33" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="J33" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K33" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="L33" s="9">
+      <c r="L33" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="M33" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N33" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O33" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P33" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q33" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="R33" s="9">
         <v>41</v>
       </c>
-      <c r="M33" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S33" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A34" s="1">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C34" s="2">
         <v>1234567890</v>
@@ -2265,40 +2896,58 @@
         <v>64</v>
       </c>
       <c r="E34" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F34" s="4">
+        <v>1234</v>
+      </c>
+      <c r="G34" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H34" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J34" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K34" s="7">
+        <v>61</v>
+      </c>
+      <c r="L34" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F34" s="4">
-        <v>1234</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H34" s="7">
-        <v>61</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="J34" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K34" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="L34" s="9">
+      <c r="M34" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N34" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O34" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P34" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q34" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="R34" s="9">
         <v>44</v>
       </c>
-      <c r="M34" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S34" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A35" s="1">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C35" s="2">
         <v>1234567890</v>
@@ -2307,40 +2956,58 @@
         <v>47</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F35" s="4">
         <v>1234</v>
       </c>
-      <c r="G35" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H35" s="7">
+      <c r="G35" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H35" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K35" s="7">
         <v>62</v>
       </c>
-      <c r="I35" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="J35" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K35" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="L35" s="9">
+      <c r="L35" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="M35" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N35" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O35" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P35" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q35" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="R35" s="9">
         <v>45</v>
       </c>
-      <c r="M35" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S35" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A36" s="1">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C36" s="2">
         <v>1234567890</v>
@@ -2349,40 +3016,58 @@
         <v>45</v>
       </c>
       <c r="E36" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F36" s="4">
+        <v>1234</v>
+      </c>
+      <c r="G36" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H36" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K36" s="7">
+        <v>63</v>
+      </c>
+      <c r="L36" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="M36" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N36" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O36" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P36" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q36" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="R36" s="9">
+        <v>42</v>
+      </c>
+      <c r="S36" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F36" s="4">
-        <v>1234</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H36" s="7">
-        <v>63</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="J36" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K36" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="L36" s="9">
-        <v>42</v>
-      </c>
-      <c r="M36" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+    </row>
+    <row r="37" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A37" s="1">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C37" s="2">
         <v>1234567890</v>
@@ -2391,40 +3076,58 @@
         <v>13</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F37" s="4">
         <v>1234</v>
       </c>
-      <c r="G37" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H37" s="7">
+      <c r="G37" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H37" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K37" s="7">
         <v>64</v>
       </c>
-      <c r="I37" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="J37" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K37" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="L37" s="9">
+      <c r="L37" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="M37" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N37" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O37" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P37" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q37" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="R37" s="9">
         <v>46</v>
       </c>
-      <c r="M37" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S37" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A38" s="1">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C38" s="2">
         <v>1234567890</v>
@@ -2433,40 +3136,58 @@
         <v>51</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F38" s="4">
         <v>1234</v>
       </c>
-      <c r="G38" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="H38" s="10">
+      <c r="G38" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H38" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J38" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="K38" s="10">
         <v>54</v>
       </c>
-      <c r="I38" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="J38" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K38" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="L38" s="11">
+      <c r="L38" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="M38" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N38" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O38" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P38" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q38" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="R38" s="11">
         <v>49</v>
       </c>
-      <c r="M38" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S38" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A39" s="1">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C39" s="2">
         <v>1234567890</v>
@@ -2475,40 +3196,58 @@
         <v>53</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F39" s="4">
         <v>1234</v>
       </c>
-      <c r="G39" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="H39" s="10">
+      <c r="G39" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H39" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J39" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="K39" s="10">
         <v>48</v>
       </c>
-      <c r="I39" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="J39" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K39" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="L39" s="11">
+      <c r="L39" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="M39" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N39" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O39" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P39" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q39" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="R39" s="11">
         <v>52</v>
       </c>
-      <c r="M39" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S39" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A40" s="1">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C40" s="2">
         <v>1234567890</v>
@@ -2517,40 +3256,58 @@
         <v>56</v>
       </c>
       <c r="E40" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F40" s="4">
+        <v>1234</v>
+      </c>
+      <c r="G40" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H40" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J40" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="K40" s="10">
+        <v>40</v>
+      </c>
+      <c r="L40" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="M40" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N40" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O40" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P40" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q40" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="R40" s="11">
+        <v>50</v>
+      </c>
+      <c r="S40" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F40" s="4">
-        <v>1234</v>
-      </c>
-      <c r="G40" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="H40" s="10">
-        <v>40</v>
-      </c>
-      <c r="I40" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="J40" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K40" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="L40" s="11">
-        <v>50</v>
-      </c>
-      <c r="M40" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+    </row>
+    <row r="41" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A41" s="1">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C41" s="2">
         <v>1234567890</v>
@@ -2559,40 +3316,58 @@
         <v>54</v>
       </c>
       <c r="E41" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F41" s="4">
+        <v>1234</v>
+      </c>
+      <c r="G41" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H41" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J41" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="K41" s="10">
+        <v>56</v>
+      </c>
+      <c r="L41" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="M41" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N41" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O41" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P41" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q41" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="R41" s="11">
+        <v>53</v>
+      </c>
+      <c r="S41" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F41" s="4">
-        <v>1234</v>
-      </c>
-      <c r="G41" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="H41" s="10">
-        <v>56</v>
-      </c>
-      <c r="I41" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="J41" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K41" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="L41" s="11">
-        <v>53</v>
-      </c>
-      <c r="M41" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+    </row>
+    <row r="42" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A42" s="1">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C42" s="2">
         <v>1234567890</v>
@@ -2601,40 +3376,58 @@
         <v>49</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F42" s="4">
         <v>1234</v>
       </c>
-      <c r="G42" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="H42" s="10">
+      <c r="G42" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H42" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J42" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="K42" s="10">
         <v>32</v>
       </c>
-      <c r="I42" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="J42" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K42" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="L42" s="11">
+      <c r="L42" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="M42" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N42" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O42" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P42" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q42" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="R42" s="11">
         <v>51</v>
       </c>
-      <c r="M42" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S42" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A43" s="1">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="B43" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C43" s="2">
         <v>1234567890</v>
@@ -2643,40 +3436,58 @@
         <v>66</v>
       </c>
       <c r="E43" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F43" s="4">
+        <v>1234</v>
+      </c>
+      <c r="G43" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H43" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J43" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="F43" s="4">
-        <v>1234</v>
-      </c>
-      <c r="G43" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="H43" s="10">
+      <c r="K43" s="10">
         <v>8</v>
-      </c>
-      <c r="I43" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="J43" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K43" s="4" t="s">
-        <v>104</v>
       </c>
       <c r="L43" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="M43" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="M43" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N43" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O43" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P43" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q43" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="R43" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="S43" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A44" s="1">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
       <c r="B44" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C44" s="2">
         <v>1234567890</v>
@@ -2685,40 +3496,58 @@
         <v>62</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F44" s="4">
         <v>1234</v>
       </c>
-      <c r="G44" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H44" s="7">
+      <c r="G44" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H44" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K44" s="7">
         <v>41</v>
       </c>
-      <c r="I44" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="J44" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K44" s="4" t="s">
-        <v>104</v>
-      </c>
       <c r="L44" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="M44" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+        <v>99</v>
+      </c>
+      <c r="M44" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N44" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O44" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P44" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q44" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="R44" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="S44" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A45" s="1">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="B45" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C45" s="2">
         <v>1234567890</v>
@@ -2727,40 +3556,58 @@
         <v>30</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F45" s="4">
         <v>1234</v>
       </c>
-      <c r="G45" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H45" s="7">
+      <c r="G45" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H45" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J45" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K45" s="7">
         <v>43</v>
       </c>
-      <c r="I45" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="J45" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K45" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="L45" s="8">
+      <c r="L45" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="M45" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N45" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O45" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P45" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q45" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="R45" s="8">
         <v>43</v>
       </c>
-      <c r="M45" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S45" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A46" s="1">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C46" s="2">
         <v>1234567890</v>
@@ -2769,40 +3616,58 @@
         <v>33</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F46" s="4">
         <v>1234</v>
       </c>
-      <c r="G46" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H46" s="7">
+      <c r="G46" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H46" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J46" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K46" s="7">
         <v>45</v>
       </c>
-      <c r="I46" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="J46" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K46" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="L46" s="8">
+      <c r="L46" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="M46" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N46" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O46" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P46" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q46" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="R46" s="8">
         <v>45</v>
       </c>
-      <c r="M46" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S46" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A47" s="1">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C47" s="2">
         <v>1234567890</v>
@@ -2811,40 +3676,58 @@
         <v>57</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F47" s="4">
         <v>1234</v>
       </c>
-      <c r="G47" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H47" s="7">
+      <c r="G47" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H47" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K47" s="7">
         <v>44</v>
       </c>
-      <c r="I47" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="J47" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K47" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="L47" s="8">
+      <c r="L47" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="M47" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N47" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O47" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P47" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q47" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="R47" s="8">
         <v>46</v>
       </c>
-      <c r="M47" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S47" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A48" s="1">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C48" s="2">
         <v>1234567890</v>
@@ -2853,40 +3736,58 @@
         <v>53</v>
       </c>
       <c r="E48" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F48" s="4">
+        <v>1234</v>
+      </c>
+      <c r="G48" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H48" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J48" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K48" s="7">
+        <v>42</v>
+      </c>
+      <c r="L48" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F48" s="4">
-        <v>1234</v>
-      </c>
-      <c r="G48" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H48" s="7">
-        <v>42</v>
-      </c>
-      <c r="I48" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="J48" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K48" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="L48" s="8">
+      <c r="M48" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N48" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O48" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P48" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q48" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="R48" s="8">
         <v>44</v>
       </c>
-      <c r="M48" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S48" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A49" s="1">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C49" s="2">
         <v>1234567890</v>
@@ -2895,40 +3796,58 @@
         <v>30</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F49" s="4">
         <v>1234</v>
       </c>
-      <c r="G49" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H49" s="7">
+      <c r="G49" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H49" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J49" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K49" s="7">
         <v>46</v>
       </c>
-      <c r="I49" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="J49" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K49" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="L49" s="8">
+      <c r="L49" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="M49" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N49" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O49" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P49" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q49" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="R49" s="8">
         <v>48</v>
       </c>
-      <c r="M49" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S49" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A50" s="1">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="B50" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C50" s="2">
         <v>1234567890</v>
@@ -2937,40 +3856,58 @@
         <v>29</v>
       </c>
       <c r="E50" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F50" s="4">
+        <v>1234</v>
+      </c>
+      <c r="G50" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H50" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J50" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="K50" s="11">
+        <v>34</v>
+      </c>
+      <c r="L50" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F50" s="4">
-        <v>1234</v>
-      </c>
-      <c r="G50" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="H50" s="11">
-        <v>34</v>
-      </c>
-      <c r="I50" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="J50" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K50" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="L50" s="8">
+      <c r="M50" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N50" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O50" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P50" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q50" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="R50" s="8">
         <v>50</v>
       </c>
-      <c r="M50" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S50" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A51" s="1">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="B51" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C51" s="2">
         <v>1234567890</v>
@@ -2979,40 +3916,58 @@
         <v>32</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F51" s="4">
         <v>1234</v>
       </c>
-      <c r="G51" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="H51" s="11">
+      <c r="G51" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H51" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J51" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="K51" s="11">
         <v>35</v>
       </c>
-      <c r="I51" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="J51" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K51" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="L51" s="8">
+      <c r="L51" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="M51" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N51" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O51" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P51" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q51" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="R51" s="8">
         <v>51</v>
       </c>
-      <c r="M51" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S51" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A52" s="1">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
       <c r="B52" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C52" s="2">
         <v>1234567890</v>
@@ -3021,40 +3976,58 @@
         <v>34</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F52" s="4">
         <v>1234</v>
       </c>
-      <c r="G52" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="H52" s="11">
+      <c r="G52" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H52" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J52" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="K52" s="11">
         <v>37</v>
       </c>
-      <c r="I52" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="J52" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K52" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="L52" s="8">
+      <c r="L52" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="M52" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N52" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O52" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P52" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q52" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="R52" s="8">
         <v>53</v>
       </c>
-      <c r="M52" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S52" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A53" s="1">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
       <c r="B53" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C53" s="2">
         <v>1234567890</v>
@@ -3063,40 +4036,58 @@
         <v>67</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F53" s="4">
         <v>1234</v>
       </c>
-      <c r="G53" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="H53" s="11">
+      <c r="G53" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H53" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="K53" s="11">
         <v>33</v>
       </c>
-      <c r="I53" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="J53" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K53" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="L53" s="8">
+      <c r="L53" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="M53" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N53" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O53" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P53" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q53" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="R53" s="8">
         <v>49</v>
       </c>
-      <c r="M53" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S53" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A54" s="1">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C54" s="2">
         <v>1234567890</v>
@@ -3105,40 +4096,58 @@
         <v>62</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F54" s="4">
         <v>1234</v>
       </c>
-      <c r="G54" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="H54" s="11">
+      <c r="G54" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H54" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J54" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="K54" s="11">
         <v>36</v>
       </c>
-      <c r="I54" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="J54" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K54" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="L54" s="8">
+      <c r="L54" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="M54" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N54" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O54" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P54" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q54" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="R54" s="8">
         <v>52</v>
       </c>
-      <c r="M54" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S54" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A55" s="1">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
       <c r="B55" s="14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C55" s="2">
         <v>1234567890</v>
@@ -3147,40 +4156,58 @@
         <v>56</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F55" s="4">
         <v>1234</v>
       </c>
-      <c r="G55" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="H55" s="11">
+      <c r="G55" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H55" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J55" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="K55" s="11">
         <v>38</v>
       </c>
-      <c r="I55" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="J55" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K55" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="L55" s="8">
+      <c r="L55" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="M55" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N55" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O55" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P55" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q55" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="R55" s="8">
         <v>54</v>
       </c>
-      <c r="M55" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S55" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A56" s="1">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
       <c r="B56" s="14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C56" s="2">
         <v>1234567890</v>
@@ -3189,40 +4216,58 @@
         <v>49</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F56" s="4">
         <v>1234</v>
       </c>
-      <c r="G56" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="H56" s="8">
+      <c r="G56" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H56" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I56" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J56" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="K56" s="8">
         <v>41</v>
       </c>
-      <c r="I56" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="J56" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K56" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L56" s="7">
+      <c r="L56" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="M56" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N56" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O56" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P56" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q56" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="R56" s="7">
         <v>44</v>
       </c>
-      <c r="M56" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S56" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A57" s="1">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
       <c r="B57" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C57" s="2">
         <v>1234567890</v>
@@ -3231,40 +4276,58 @@
         <v>56</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F57" s="4">
         <v>1234</v>
       </c>
-      <c r="G57" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="H57" s="8">
+      <c r="G57" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H57" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J57" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="K57" s="8">
         <v>43</v>
       </c>
-      <c r="I57" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="J57" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K57" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L57" s="7">
+      <c r="L57" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="M57" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N57" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O57" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P57" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q57" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="R57" s="7">
         <v>43</v>
       </c>
-      <c r="M57" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S57" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A58" s="1">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
       <c r="B58" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C58" s="2">
         <v>1234567890</v>
@@ -3273,40 +4336,58 @@
         <v>52</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F58" s="4">
         <v>1234</v>
       </c>
-      <c r="G58" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="H58" s="8">
+      <c r="G58" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H58" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I58" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J58" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="K58" s="8">
         <v>44</v>
       </c>
-      <c r="I58" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="J58" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K58" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L58" s="7">
+      <c r="L58" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="M58" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N58" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O58" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P58" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q58" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="R58" s="7">
         <v>46</v>
       </c>
-      <c r="M58" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S58" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A59" s="1">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
       <c r="B59" s="14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C59" s="2">
         <v>1234567890</v>
@@ -3315,40 +4396,58 @@
         <v>48</v>
       </c>
       <c r="E59" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F59" s="4">
+        <v>1234</v>
+      </c>
+      <c r="G59" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H59" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I59" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J59" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="K59" s="8">
+        <v>42</v>
+      </c>
+      <c r="L59" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F59" s="4">
-        <v>1234</v>
-      </c>
-      <c r="G59" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="H59" s="8">
+      <c r="M59" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N59" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O59" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P59" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q59" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="R59" s="7">
         <v>42</v>
       </c>
-      <c r="I59" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="J59" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K59" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L59" s="7">
-        <v>42</v>
-      </c>
-      <c r="M59" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S59" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A60" s="1">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C60" s="2">
         <v>1234567890</v>
@@ -3357,40 +4456,58 @@
         <v>59</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F60" s="4">
         <v>1234</v>
       </c>
-      <c r="G60" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="H60" s="8">
+      <c r="G60" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H60" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I60" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J60" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="K60" s="8">
         <v>46</v>
       </c>
-      <c r="I60" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="J60" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K60" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L60" s="7">
+      <c r="L60" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="M60" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N60" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O60" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P60" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q60" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="R60" s="7">
         <v>48</v>
       </c>
-      <c r="M60" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S60" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A61" s="1">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C61" s="2">
         <v>1234567890</v>
@@ -3399,40 +4516,58 @@
         <v>56</v>
       </c>
       <c r="E61" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F61" s="4">
+        <v>1234</v>
+      </c>
+      <c r="G61" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H61" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J61" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="K61" s="8">
+        <v>45</v>
+      </c>
+      <c r="L61" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F61" s="4">
-        <v>1234</v>
-      </c>
-      <c r="G61" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="H61" s="8">
+      <c r="M61" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N61" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O61" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P61" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q61" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="R61" s="7">
         <v>45</v>
       </c>
-      <c r="I61" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="J61" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K61" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L61" s="7">
-        <v>45</v>
-      </c>
-      <c r="M61" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S61" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A62" s="1">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C62" s="2">
         <v>1234567890</v>
@@ -3441,40 +4576,58 @@
         <v>59</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F62" s="4">
         <v>1234</v>
       </c>
-      <c r="G62" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="H62" s="9">
+      <c r="G62" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H62" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I62" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J62" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="K62" s="9">
         <v>66</v>
       </c>
-      <c r="I62" s="4" t="s">
+      <c r="L62" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="M62" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N62" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O62" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P62" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q62" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="R62" s="9">
+        <v>51</v>
+      </c>
+      <c r="S62" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="J62" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K62" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="L62" s="9">
-        <v>51</v>
-      </c>
-      <c r="M62" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+    </row>
+    <row r="63" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A63" s="1">
         <f>A62+1</f>
         <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C63" s="2">
         <v>1234567890</v>
@@ -3483,40 +4636,58 @@
         <v>56</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F63" s="4">
         <v>1234</v>
       </c>
-      <c r="G63" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="H63" s="9">
+      <c r="G63" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H63" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I63" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J63" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="K63" s="9">
         <v>67</v>
       </c>
-      <c r="I63" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="J63" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K63" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="L63" s="9">
+      <c r="L63" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="M63" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N63" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O63" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P63" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q63" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="R63" s="9">
         <v>49</v>
       </c>
-      <c r="M63" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S63" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A64" s="1">
         <f>A63+1</f>
         <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C64" s="2">
         <v>1234567890</v>
@@ -3525,40 +4696,58 @@
         <v>75</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F64" s="4">
         <v>1234</v>
       </c>
-      <c r="G64" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="H64" s="9">
+      <c r="G64" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H64" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I64" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J64" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="K64" s="9">
         <v>69</v>
       </c>
-      <c r="I64" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="J64" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K64" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="L64" s="9">
+      <c r="L64" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="M64" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N64" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O64" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P64" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q64" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="R64" s="9">
         <v>52</v>
       </c>
-      <c r="M64" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S64" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A65" s="1">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C65" s="2">
         <v>1234567890</v>
@@ -3567,40 +4756,58 @@
         <v>65</v>
       </c>
       <c r="E65" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F65" s="4">
+        <v>1234</v>
+      </c>
+      <c r="G65" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H65" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I65" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J65" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="K65" s="9">
+        <v>70</v>
+      </c>
+      <c r="L65" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="M65" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N65" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O65" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P65" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q65" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="R65" s="9">
+        <v>50</v>
+      </c>
+      <c r="S65" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F65" s="4">
-        <v>1234</v>
-      </c>
-      <c r="G65" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="H65" s="9">
-        <v>70</v>
-      </c>
-      <c r="I65" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="J65" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K65" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="L65" s="9">
-        <v>50</v>
-      </c>
-      <c r="M65" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+    </row>
+    <row r="66" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A66" s="1">
         <f>A65+1</f>
         <v>65</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C66" s="2">
         <v>1234567890</v>
@@ -3609,40 +4816,58 @@
         <v>58</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F66" s="4">
         <v>1234</v>
       </c>
-      <c r="G66" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="H66" s="9">
+      <c r="G66" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H66" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I66" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J66" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="K66" s="9">
         <v>72</v>
       </c>
-      <c r="I66" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="J66" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K66" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="L66" s="9">
+      <c r="L66" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="M66" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N66" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O66" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P66" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q66" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="R66" s="9">
         <v>54</v>
       </c>
-      <c r="M66" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S66" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A67" s="1">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C67" s="2">
         <v>1234567890</v>
@@ -3651,40 +4876,58 @@
         <v>57</v>
       </c>
       <c r="E67" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F67" s="4">
+        <v>1234</v>
+      </c>
+      <c r="G67" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H67" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I67" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J67" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="K67" s="9">
+        <v>71</v>
+      </c>
+      <c r="L67" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="M67" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N67" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O67" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P67" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q67" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="R67" s="9">
+        <v>53</v>
+      </c>
+      <c r="S67" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F67" s="4">
-        <v>1234</v>
-      </c>
-      <c r="G67" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="H67" s="9">
-        <v>71</v>
-      </c>
-      <c r="I67" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="J67" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K67" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="L67" s="9">
-        <v>53</v>
-      </c>
-      <c r="M67" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+    </row>
+    <row r="68" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A68" s="1">
         <f t="shared" ref="A68:A80" si="1">A67+1</f>
         <v>67</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C68" s="2">
         <v>1234567890</v>
@@ -3693,40 +4936,58 @@
         <v>29</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F68" s="4">
         <v>1234</v>
       </c>
-      <c r="G68" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="H68" s="9">
+      <c r="G68" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H68" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I68" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J68" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="K68" s="9">
         <v>58</v>
       </c>
-      <c r="I68" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="J68" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K68" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L68" s="7">
+      <c r="L68" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="M68" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N68" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O68" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P68" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q68" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="R68" s="7">
         <v>8</v>
       </c>
-      <c r="M68" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S68" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A69" s="1">
         <f t="shared" si="1"/>
         <v>68</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C69" s="2">
         <v>1234567890</v>
@@ -3735,40 +4996,58 @@
         <v>68</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F69" s="4">
         <v>1234</v>
       </c>
-      <c r="G69" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="H69" s="9">
+      <c r="G69" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H69" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I69" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J69" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="K69" s="9">
         <v>59</v>
       </c>
-      <c r="I69" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="J69" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K69" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L69" s="7">
+      <c r="L69" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="M69" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N69" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O69" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P69" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q69" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="R69" s="7">
         <v>36</v>
       </c>
-      <c r="M69" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S69" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A70" s="1">
         <f t="shared" si="1"/>
         <v>69</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C70" s="2">
         <v>1234567890</v>
@@ -3777,40 +5056,58 @@
         <v>56</v>
       </c>
       <c r="E70" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F70" s="4">
+        <v>1234</v>
+      </c>
+      <c r="G70" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H70" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I70" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J70" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="K70" s="9">
+        <v>61</v>
+      </c>
+      <c r="L70" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F70" s="4">
-        <v>1234</v>
-      </c>
-      <c r="G70" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="H70" s="9">
-        <v>61</v>
-      </c>
-      <c r="I70" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="J70" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K70" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L70" s="7">
+      <c r="M70" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N70" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O70" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P70" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q70" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="R70" s="7">
         <v>37</v>
       </c>
-      <c r="M70" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S70" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A71" s="1">
         <f t="shared" si="1"/>
         <v>70</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C71" s="2">
         <v>7709506569</v>
@@ -3819,40 +5116,58 @@
         <v>33</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F71" s="4">
         <v>1234</v>
       </c>
-      <c r="G71" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="H71" s="9">
+      <c r="G71" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H71" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I71" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J71" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="K71" s="9">
         <v>62</v>
       </c>
-      <c r="I71" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="J71" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K71" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L71" s="7">
+      <c r="L71" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="M71" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N71" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O71" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P71" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q71" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="R71" s="7">
         <v>38</v>
       </c>
-      <c r="M71" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S71" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A72" s="1">
         <f t="shared" si="1"/>
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C72" s="2">
         <v>1234567890</v>
@@ -3861,40 +5176,58 @@
         <v>30</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F72" s="4">
         <v>1234</v>
       </c>
-      <c r="G72" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="H72" s="9">
+      <c r="G72" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H72" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I72" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J72" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="K72" s="9">
         <v>64</v>
       </c>
-      <c r="I72" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="J72" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K72" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L72" s="7">
+      <c r="L72" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="M72" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N72" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O72" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P72" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q72" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="R72" s="7">
         <v>40</v>
       </c>
-      <c r="M72" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S72" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A73" s="1">
         <f t="shared" si="1"/>
         <v>72</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C73" s="2">
         <v>1234567890</v>
@@ -3903,40 +5236,58 @@
         <v>66</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F73" s="4">
         <v>1234</v>
       </c>
-      <c r="G73" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="H73" s="9">
+      <c r="G73" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H73" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I73" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J73" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="K73" s="9">
         <v>63</v>
       </c>
-      <c r="I73" s="4" t="s">
+      <c r="L73" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="M73" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N73" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O73" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P73" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q73" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="R73" s="7">
+        <v>41</v>
+      </c>
+      <c r="S73" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="J73" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K73" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L73" s="7">
-        <v>41</v>
-      </c>
-      <c r="M73" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+    </row>
+    <row r="74" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A74" s="1">
         <f t="shared" si="1"/>
         <v>73</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C74" s="2">
         <v>1234567890</v>
@@ -3945,40 +5296,58 @@
         <v>57</v>
       </c>
       <c r="E74" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F74" s="4">
+        <v>1234</v>
+      </c>
+      <c r="G74" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H74" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I74" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J74" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="K74" s="8">
+        <v>18</v>
+      </c>
+      <c r="L74" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F74" s="4">
-        <v>1234</v>
-      </c>
-      <c r="G74" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="H74" s="8">
-        <v>18</v>
-      </c>
-      <c r="I74" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="J74" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K74" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="L74" s="9">
+      <c r="M74" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N74" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O74" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P74" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q74" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="R74" s="9">
         <v>33</v>
       </c>
-      <c r="M74" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S74" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A75" s="1">
         <f t="shared" si="1"/>
         <v>74</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C75" s="2">
         <v>1234567890</v>
@@ -3987,40 +5356,58 @@
         <v>32</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F75" s="4">
         <v>1234</v>
       </c>
-      <c r="G75" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="H75" s="8">
+      <c r="G75" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H75" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I75" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J75" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="K75" s="8">
         <v>19</v>
       </c>
-      <c r="I75" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="J75" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K75" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="L75" s="9">
+      <c r="L75" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="M75" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N75" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O75" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P75" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q75" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="R75" s="9">
         <v>35</v>
       </c>
-      <c r="M75" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S75" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A76" s="1">
         <f t="shared" si="1"/>
         <v>75</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C76" s="2">
         <v>1234567890</v>
@@ -4029,40 +5416,58 @@
         <v>30</v>
       </c>
       <c r="E76" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F76" s="4">
+        <v>1234</v>
+      </c>
+      <c r="G76" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H76" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I76" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J76" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="K76" s="8">
+        <v>21</v>
+      </c>
+      <c r="L76" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F76" s="4">
-        <v>1234</v>
-      </c>
-      <c r="G76" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="H76" s="8">
-        <v>21</v>
-      </c>
-      <c r="I76" s="4" t="s">
+      <c r="M76" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N76" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O76" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P76" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q76" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="R76" s="9">
+        <v>38</v>
+      </c>
+      <c r="S76" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="J76" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K76" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="L76" s="9">
-        <v>38</v>
-      </c>
-      <c r="M76" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+    </row>
+    <row r="77" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A77" s="1">
         <f t="shared" si="1"/>
         <v>76</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C77" s="2">
         <v>1234567890</v>
@@ -4071,40 +5476,58 @@
         <v>75</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F77" s="4">
         <v>1234</v>
       </c>
-      <c r="G77" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="H77" s="8">
+      <c r="G77" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H77" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I77" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J77" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="K77" s="8">
         <v>17</v>
       </c>
-      <c r="I77" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="J77" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K77" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="L77" s="9">
+      <c r="L77" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="M77" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N77" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O77" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P77" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q77" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="R77" s="9">
         <v>36</v>
       </c>
-      <c r="M77" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S77" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A78" s="1">
         <f t="shared" si="1"/>
         <v>77</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C78" s="2">
         <v>1234567890</v>
@@ -4113,40 +5536,58 @@
         <v>72</v>
       </c>
       <c r="E78" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F78" s="4">
+        <v>1234</v>
+      </c>
+      <c r="G78" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H78" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I78" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J78" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="K78" s="8">
+        <v>23</v>
+      </c>
+      <c r="L78" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="M78" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N78" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O78" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P78" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q78" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="R78" s="9">
+        <v>34</v>
+      </c>
+      <c r="S78" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F78" s="4">
-        <v>1234</v>
-      </c>
-      <c r="G78" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="H78" s="8">
-        <v>23</v>
-      </c>
-      <c r="I78" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="J78" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K78" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="L78" s="9">
-        <v>34</v>
-      </c>
-      <c r="M78" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+    </row>
+    <row r="79" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A79" s="1">
         <f t="shared" si="1"/>
         <v>78</v>
       </c>
       <c r="B79" s="14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C79" s="2">
         <v>1234567890</v>
@@ -4155,40 +5596,58 @@
         <v>67</v>
       </c>
       <c r="E79" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F79" s="4">
+        <v>1234</v>
+      </c>
+      <c r="G79" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H79" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I79" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J79" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="K79" s="8">
+        <v>20</v>
+      </c>
+      <c r="L79" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="M79" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N79" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O79" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P79" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q79" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="R79" s="9">
+        <v>37</v>
+      </c>
+      <c r="S79" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F79" s="4">
-        <v>1234</v>
-      </c>
-      <c r="G79" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="H79" s="8">
-        <v>20</v>
-      </c>
-      <c r="I79" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="J79" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K79" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="L79" s="9">
-        <v>37</v>
-      </c>
-      <c r="M79" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+    </row>
+    <row r="80" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A80" s="1">
         <f t="shared" si="1"/>
         <v>79</v>
       </c>
       <c r="B80" s="14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C80" s="2">
         <v>1234567890</v>
@@ -4197,40 +5656,58 @@
         <v>70</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F80" s="4">
         <v>1234</v>
       </c>
-      <c r="G80" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H80" s="7">
+      <c r="G80" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H80" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I80" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J80" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K80" s="7">
         <v>36</v>
       </c>
-      <c r="I80" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="J80" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K80" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L80" s="7">
+      <c r="L80" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="M80" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N80" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O80" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P80" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q80" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="R80" s="7">
         <v>1</v>
       </c>
-      <c r="M80" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S80" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A81" s="1">
         <f>A80+1</f>
         <v>80</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C81" s="2">
         <v>1234567890</v>
@@ -4239,40 +5716,58 @@
         <v>72</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F81" s="4">
         <v>1234</v>
       </c>
-      <c r="G81" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H81" s="7">
+      <c r="G81" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H81" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I81" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J81" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K81" s="7">
         <v>35</v>
       </c>
-      <c r="I81" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="J81" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K81" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L81" s="7">
+      <c r="L81" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="M81" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N81" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O81" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P81" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q81" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="R81" s="7">
         <v>4</v>
       </c>
-      <c r="M81" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S81" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A82" s="1">
         <f>A81+1</f>
         <v>81</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C82" s="2">
         <v>1234567890</v>
@@ -4281,40 +5776,58 @@
         <v>69</v>
       </c>
       <c r="E82" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F82" s="4">
+        <v>1234</v>
+      </c>
+      <c r="G82" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H82" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I82" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J82" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K82" s="7">
+        <v>37</v>
+      </c>
+      <c r="L82" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F82" s="4">
-        <v>1234</v>
-      </c>
-      <c r="G82" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H82" s="7">
-        <v>37</v>
-      </c>
-      <c r="I82" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="J82" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K82" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L82" s="7">
+      <c r="M82" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N82" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O82" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P82" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q82" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="R82" s="7">
         <v>2</v>
       </c>
-      <c r="M82" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S82" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A83" s="1">
         <f>A82+1</f>
         <v>82</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C83" s="2">
         <v>1234567890</v>
@@ -4323,40 +5836,58 @@
         <v>25</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F83" s="4">
         <v>1234</v>
       </c>
-      <c r="G83" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H83" s="7">
+      <c r="G83" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H83" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I83" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J83" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K83" s="7">
         <v>38</v>
       </c>
-      <c r="I83" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="J83" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K83" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L83" s="7">
+      <c r="L83" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="M83" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N83" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O83" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P83" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q83" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="R83" s="7">
         <v>3</v>
       </c>
-      <c r="M83" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S83" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A84" s="1">
         <f t="shared" ref="A84:A87" si="2">A83+1</f>
         <v>83</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C84" s="2">
         <v>1234567890</v>
@@ -4365,40 +5896,58 @@
         <v>51</v>
       </c>
       <c r="E84" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F84" s="4">
+        <v>1234</v>
+      </c>
+      <c r="G84" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H84" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I84" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J84" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K84" s="7">
+        <v>40</v>
+      </c>
+      <c r="L84" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="M84" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N84" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O84" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P84" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q84" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="R84" s="7">
+        <v>5</v>
+      </c>
+      <c r="S84" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F84" s="4">
-        <v>1234</v>
-      </c>
-      <c r="G84" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H84" s="7">
-        <v>40</v>
-      </c>
-      <c r="I84" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="J84" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K84" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L84" s="7">
-        <v>5</v>
-      </c>
-      <c r="M84" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+    </row>
+    <row r="85" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A85" s="1">
         <f t="shared" si="2"/>
         <v>84</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C85" s="2">
         <v>1234567890</v>
@@ -4407,40 +5956,58 @@
         <v>23</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F85" s="4">
         <v>1234</v>
       </c>
-      <c r="G85" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H85" s="7">
+      <c r="G85" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H85" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I85" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J85" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K85" s="7">
         <v>48</v>
       </c>
-      <c r="I85" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="J85" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K85" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L85" s="7">
+      <c r="L85" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="M85" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N85" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O85" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P85" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q85" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="R85" s="7">
         <v>6</v>
       </c>
-      <c r="M85" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S85" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A86" s="1">
         <f t="shared" si="2"/>
         <v>85</v>
       </c>
       <c r="B86" s="14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C86" s="2">
         <v>1234567890</v>
@@ -4449,40 +6016,58 @@
         <v>51</v>
       </c>
       <c r="E86" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F86" s="4">
+        <v>1234</v>
+      </c>
+      <c r="G86" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H86" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I86" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J86" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K86" s="7">
+        <v>66</v>
+      </c>
+      <c r="L86" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F86" s="4">
-        <v>1234</v>
-      </c>
-      <c r="G86" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H86" s="7">
-        <v>66</v>
-      </c>
-      <c r="I86" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="J86" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K86" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L86" s="7">
+      <c r="M86" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N86" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O86" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P86" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q86" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="R86" s="7">
         <v>17</v>
       </c>
-      <c r="M86" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S86" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A87" s="1">
         <f t="shared" si="2"/>
         <v>86</v>
       </c>
       <c r="B87" s="14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C87" s="2">
         <v>1234567890</v>
@@ -4491,40 +6076,58 @@
         <v>55</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F87" s="4">
         <v>1234</v>
       </c>
-      <c r="G87" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H87" s="7">
+      <c r="G87" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H87" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I87" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J87" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K87" s="7">
         <v>67</v>
       </c>
-      <c r="I87" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="J87" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K87" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L87" s="7">
+      <c r="L87" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="M87" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N87" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O87" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P87" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q87" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="R87" s="7">
         <v>20</v>
       </c>
-      <c r="M87" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S87" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A88" s="1">
         <f>A87+1</f>
         <v>87</v>
       </c>
       <c r="B88" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C88" s="2">
         <v>1234567890</v>
@@ -4533,40 +6136,58 @@
         <v>75</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F88" s="4">
         <v>1234</v>
       </c>
-      <c r="G88" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H88" s="7">
+      <c r="G88" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H88" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I88" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J88" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K88" s="7">
         <v>69</v>
       </c>
-      <c r="I88" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="J88" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K88" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L88" s="7">
+      <c r="L88" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="M88" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N88" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O88" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P88" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q88" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="R88" s="7">
         <v>18</v>
       </c>
-      <c r="M88" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S88" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A89" s="1">
         <f>A88+1</f>
         <v>88</v>
       </c>
       <c r="B89" s="14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C89" s="2">
         <v>1234567890</v>
@@ -4575,40 +6196,58 @@
         <v>67</v>
       </c>
       <c r="E89" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="F89" s="4">
+        <v>1234</v>
+      </c>
+      <c r="G89" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H89" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I89" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J89" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K89" s="7">
+        <v>71</v>
+      </c>
+      <c r="L89" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="M89" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N89" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O89" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P89" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q89" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="R89" s="7">
+        <v>21</v>
+      </c>
+      <c r="S89" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F89" s="4">
-        <v>1234</v>
-      </c>
-      <c r="G89" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H89" s="7">
-        <v>71</v>
-      </c>
-      <c r="I89" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="J89" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K89" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L89" s="7">
-        <v>21</v>
-      </c>
-      <c r="M89" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+    </row>
+    <row r="90" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A90" s="1">
         <f>A89+1</f>
         <v>89</v>
       </c>
       <c r="B90" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C90" s="2">
         <v>1234567890</v>
@@ -4617,40 +6256,58 @@
         <v>70</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F90" s="4">
         <v>1234</v>
       </c>
-      <c r="G90" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H90" s="7">
+      <c r="G90" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H90" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I90" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J90" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K90" s="7">
         <v>70</v>
       </c>
-      <c r="I90" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="J90" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K90" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L90" s="7">
+      <c r="L90" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="M90" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N90" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O90" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P90" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q90" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="R90" s="7">
         <v>19</v>
       </c>
-      <c r="M90" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="91" spans="1:13" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="S90" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
       <c r="A91" s="1">
         <f>A90+1</f>
         <v>90</v>
       </c>
       <c r="B91" s="14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C91" s="2">
         <v>1234567890</v>
@@ -4659,34 +6316,53 @@
         <v>62</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F91" s="4">
         <v>1234</v>
       </c>
-      <c r="G91" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H91" s="7">
+      <c r="G91" s="15">
+        <v>46230</v>
+      </c>
+      <c r="H91" s="17">
+        <v>1234</v>
+      </c>
+      <c r="I91" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="J91" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K91" s="7">
         <v>72</v>
       </c>
-      <c r="I91" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="J91" s="6">
-        <v>4321</v>
-      </c>
-      <c r="K91" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="L91" s="7">
+      <c r="L91" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="M91" s="6">
+        <v>4321</v>
+      </c>
+      <c r="N91" s="16">
+        <v>46232</v>
+      </c>
+      <c r="O91" s="18">
+        <v>4321</v>
+      </c>
+      <c r="P91" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q91" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="R91" s="7">
         <v>7</v>
       </c>
-      <c r="M91" s="4" t="s">
-        <v>99</v>
+      <c r="S91" s="4" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/passengers.xlsx
+++ b/data/passengers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git Workspace\chaitya-paripati-2026-\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90ABEABC-9C37-4DAE-B184-A462201B692D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F728FF2A-5003-4C6A-B019-31C92DD39A32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{6314CF59-B62F-4ABE-803E-B3252DC11DF7}"/>
   </bookViews>
@@ -375,18 +375,12 @@
     <t>Seatno</t>
   </si>
   <si>
-    <t>Birth</t>
-  </si>
-  <si>
     <t>Return Coach</t>
   </si>
   <si>
     <t>Return Seatno</t>
   </si>
   <si>
-    <t>Return Birth</t>
-  </si>
-  <si>
     <t>Surat to Pune (Date)</t>
   </si>
   <si>
@@ -412,6 +406,12 @@
   </si>
   <si>
     <t>TrainNoR</t>
+  </si>
+  <si>
+    <t>Berth</t>
+  </si>
+  <si>
+    <t>BerthR</t>
   </si>
 </sst>
 </file>
@@ -920,16 +920,16 @@
         <v>111</v>
       </c>
       <c r="F1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="J1" t="s">
         <v>2</v>
@@ -938,28 +938,28 @@
         <v>112</v>
       </c>
       <c r="L1" t="s">
+        <v>124</v>
+      </c>
+      <c r="M1" t="s">
+        <v>115</v>
+      </c>
+      <c r="N1" t="s">
+        <v>120</v>
+      </c>
+      <c r="O1" t="s">
+        <v>123</v>
+      </c>
+      <c r="P1" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q1" t="s">
         <v>113</v>
       </c>
-      <c r="M1" t="s">
-        <v>117</v>
-      </c>
-      <c r="N1" t="s">
-        <v>122</v>
-      </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
+        <v>114</v>
+      </c>
+      <c r="S1" t="s">
         <v>125</v>
-      </c>
-      <c r="P1" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>114</v>
-      </c>
-      <c r="R1" t="s">
-        <v>115</v>
-      </c>
-      <c r="S1" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="15.75" x14ac:dyDescent="0.45">
@@ -988,7 +988,7 @@
         <v>1234</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>97</v>
@@ -1009,7 +1009,7 @@
         <v>4321</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q2" s="7" t="s">
         <v>93</v>
@@ -1048,7 +1048,7 @@
         <v>1234</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J3" s="5" t="s">
         <v>97</v>
@@ -1069,7 +1069,7 @@
         <v>4321</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q3" s="7" t="s">
         <v>93</v>
@@ -1108,7 +1108,7 @@
         <v>1234</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J4" s="5" t="s">
         <v>97</v>
@@ -1129,7 +1129,7 @@
         <v>4321</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q4" s="4" t="s">
         <v>103</v>
@@ -1168,7 +1168,7 @@
         <v>1234</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>97</v>
@@ -1189,7 +1189,7 @@
         <v>4321</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q5" s="4" t="s">
         <v>103</v>
@@ -1228,7 +1228,7 @@
         <v>1234</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>97</v>
@@ -1249,7 +1249,7 @@
         <v>4321</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q6" s="7" t="s">
         <v>93</v>
@@ -1288,7 +1288,7 @@
         <v>1234</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>97</v>
@@ -1309,7 +1309,7 @@
         <v>4321</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q7" s="7" t="s">
         <v>93</v>
@@ -1348,7 +1348,7 @@
         <v>1234</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J8" s="8" t="s">
         <v>105</v>
@@ -1369,7 +1369,7 @@
         <v>4321</v>
       </c>
       <c r="P8" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q8" s="7" t="s">
         <v>93</v>
@@ -1408,7 +1408,7 @@
         <v>1234</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J9" s="8" t="s">
         <v>105</v>
@@ -1429,7 +1429,7 @@
         <v>4321</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q9" s="4" t="s">
         <v>103</v>
@@ -1468,7 +1468,7 @@
         <v>1234</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>105</v>
@@ -1489,7 +1489,7 @@
         <v>4321</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q10" s="4" t="s">
         <v>103</v>
@@ -1528,7 +1528,7 @@
         <v>1234</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J11" s="8" t="s">
         <v>105</v>
@@ -1549,7 +1549,7 @@
         <v>4321</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q11" s="4" t="s">
         <v>103</v>
@@ -1588,7 +1588,7 @@
         <v>1234</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>105</v>
@@ -1609,7 +1609,7 @@
         <v>4321</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q12" s="7" t="s">
         <v>93</v>
@@ -1648,7 +1648,7 @@
         <v>1234</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J13" s="8" t="s">
         <v>105</v>
@@ -1669,7 +1669,7 @@
         <v>4321</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q13" s="8" t="s">
         <v>105</v>
@@ -1708,7 +1708,7 @@
         <v>1234</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J14" s="7" t="s">
         <v>93</v>
@@ -1729,7 +1729,7 @@
         <v>4321</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q14" s="9" t="s">
         <v>95</v>
@@ -1768,7 +1768,7 @@
         <v>1234</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J15" s="7" t="s">
         <v>93</v>
@@ -1789,7 +1789,7 @@
         <v>4321</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q15" s="9" t="s">
         <v>95</v>
@@ -1828,7 +1828,7 @@
         <v>1234</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J16" s="7" t="s">
         <v>93</v>
@@ -1849,7 +1849,7 @@
         <v>4321</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q16" s="9" t="s">
         <v>95</v>
@@ -1888,7 +1888,7 @@
         <v>1234</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J17" s="7" t="s">
         <v>93</v>
@@ -1909,7 +1909,7 @@
         <v>4321</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q17" s="9" t="s">
         <v>95</v>
@@ -1948,7 +1948,7 @@
         <v>1234</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J18" s="7" t="s">
         <v>93</v>
@@ -1969,7 +1969,7 @@
         <v>4321</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q18" s="9" t="s">
         <v>95</v>
@@ -2008,7 +2008,7 @@
         <v>1234</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J19" s="7" t="s">
         <v>93</v>
@@ -2029,7 +2029,7 @@
         <v>4321</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q19" s="9" t="s">
         <v>95</v>
@@ -2068,7 +2068,7 @@
         <v>1234</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J20" s="10" t="s">
         <v>97</v>
@@ -2089,7 +2089,7 @@
         <v>4321</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q20" s="11" t="s">
         <v>106</v>
@@ -2128,7 +2128,7 @@
         <v>1234</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J21" s="10" t="s">
         <v>97</v>
@@ -2149,7 +2149,7 @@
         <v>4321</v>
       </c>
       <c r="P21" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q21" s="11" t="s">
         <v>106</v>
@@ -2188,7 +2188,7 @@
         <v>1234</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>97</v>
@@ -2209,7 +2209,7 @@
         <v>4321</v>
       </c>
       <c r="P22" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q22" s="12" t="s">
         <v>106</v>
@@ -2248,7 +2248,7 @@
         <v>1234</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J23" s="10" t="s">
         <v>97</v>
@@ -2269,7 +2269,7 @@
         <v>4321</v>
       </c>
       <c r="P23" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q23" s="11" t="s">
         <v>106</v>
@@ -2308,7 +2308,7 @@
         <v>1234</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J24" s="10" t="s">
         <v>97</v>
@@ -2329,7 +2329,7 @@
         <v>4321</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q24" s="11" t="s">
         <v>106</v>
@@ -2368,7 +2368,7 @@
         <v>1234</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J25" s="10" t="s">
         <v>97</v>
@@ -2389,7 +2389,7 @@
         <v>4321</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q25" s="11" t="s">
         <v>106</v>
@@ -2428,7 +2428,7 @@
         <v>1234</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J26" s="13" t="s">
         <v>94</v>
@@ -2449,7 +2449,7 @@
         <v>4321</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q26" s="13" t="s">
         <v>95</v>
@@ -2488,7 +2488,7 @@
         <v>1234</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J27" s="13" t="s">
         <v>94</v>
@@ -2509,7 +2509,7 @@
         <v>4321</v>
       </c>
       <c r="P27" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q27" s="13" t="s">
         <v>95</v>
@@ -2548,7 +2548,7 @@
         <v>1234</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J28" s="13" t="s">
         <v>94</v>
@@ -2569,7 +2569,7 @@
         <v>4321</v>
       </c>
       <c r="P28" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q28" s="13" t="s">
         <v>95</v>
@@ -2608,7 +2608,7 @@
         <v>1234</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>94</v>
@@ -2629,7 +2629,7 @@
         <v>4321</v>
       </c>
       <c r="P29" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q29" s="13" t="s">
         <v>95</v>
@@ -2668,7 +2668,7 @@
         <v>1234</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>94</v>
@@ -2689,7 +2689,7 @@
         <v>4321</v>
       </c>
       <c r="P30" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q30" s="13" t="s">
         <v>95</v>
@@ -2728,7 +2728,7 @@
         <v>1234</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>94</v>
@@ -2749,7 +2749,7 @@
         <v>4321</v>
       </c>
       <c r="P31" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q31" s="13" t="s">
         <v>95</v>
@@ -2788,7 +2788,7 @@
         <v>1234</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J32" s="7" t="s">
         <v>93</v>
@@ -2809,7 +2809,7 @@
         <v>4321</v>
       </c>
       <c r="P32" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q32" s="9" t="s">
         <v>95</v>
@@ -2848,7 +2848,7 @@
         <v>1234</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J33" s="7" t="s">
         <v>93</v>
@@ -2869,7 +2869,7 @@
         <v>4321</v>
       </c>
       <c r="P33" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q33" s="9" t="s">
         <v>95</v>
@@ -2908,7 +2908,7 @@
         <v>1234</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J34" s="7" t="s">
         <v>93</v>
@@ -2929,7 +2929,7 @@
         <v>4321</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q34" s="9" t="s">
         <v>95</v>
@@ -2968,7 +2968,7 @@
         <v>1234</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J35" s="7" t="s">
         <v>93</v>
@@ -2989,7 +2989,7 @@
         <v>4321</v>
       </c>
       <c r="P35" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q35" s="9" t="s">
         <v>95</v>
@@ -3028,7 +3028,7 @@
         <v>1234</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J36" s="7" t="s">
         <v>93</v>
@@ -3049,7 +3049,7 @@
         <v>4321</v>
       </c>
       <c r="P36" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q36" s="9" t="s">
         <v>95</v>
@@ -3088,7 +3088,7 @@
         <v>1234</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J37" s="7" t="s">
         <v>93</v>
@@ -3109,7 +3109,7 @@
         <v>4321</v>
       </c>
       <c r="P37" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q37" s="9" t="s">
         <v>95</v>
@@ -3148,7 +3148,7 @@
         <v>1234</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J38" s="10" t="s">
         <v>97</v>
@@ -3169,7 +3169,7 @@
         <v>4321</v>
       </c>
       <c r="P38" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q38" s="11" t="s">
         <v>106</v>
@@ -3208,7 +3208,7 @@
         <v>1234</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J39" s="10" t="s">
         <v>97</v>
@@ -3229,7 +3229,7 @@
         <v>4321</v>
       </c>
       <c r="P39" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q39" s="11" t="s">
         <v>106</v>
@@ -3268,7 +3268,7 @@
         <v>1234</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J40" s="10" t="s">
         <v>97</v>
@@ -3289,7 +3289,7 @@
         <v>4321</v>
       </c>
       <c r="P40" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q40" s="11" t="s">
         <v>106</v>
@@ -3328,7 +3328,7 @@
         <v>1234</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J41" s="10" t="s">
         <v>97</v>
@@ -3349,7 +3349,7 @@
         <v>4321</v>
       </c>
       <c r="P41" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q41" s="11" t="s">
         <v>106</v>
@@ -3388,7 +3388,7 @@
         <v>1234</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J42" s="10" t="s">
         <v>97</v>
@@ -3409,7 +3409,7 @@
         <v>4321</v>
       </c>
       <c r="P42" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q42" s="11" t="s">
         <v>106</v>
@@ -3448,7 +3448,7 @@
         <v>1234</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J43" s="10" t="s">
         <v>97</v>
@@ -3469,7 +3469,7 @@
         <v>4321</v>
       </c>
       <c r="P43" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q43" s="4" t="s">
         <v>103</v>
@@ -3508,7 +3508,7 @@
         <v>1234</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J44" s="7" t="s">
         <v>93</v>
@@ -3529,7 +3529,7 @@
         <v>4321</v>
       </c>
       <c r="P44" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q44" s="4" t="s">
         <v>103</v>
@@ -3568,7 +3568,7 @@
         <v>1234</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J45" s="7" t="s">
         <v>93</v>
@@ -3589,7 +3589,7 @@
         <v>4321</v>
       </c>
       <c r="P45" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q45" s="8" t="s">
         <v>105</v>
@@ -3628,7 +3628,7 @@
         <v>1234</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J46" s="7" t="s">
         <v>93</v>
@@ -3649,7 +3649,7 @@
         <v>4321</v>
       </c>
       <c r="P46" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q46" s="8" t="s">
         <v>105</v>
@@ -3688,7 +3688,7 @@
         <v>1234</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J47" s="7" t="s">
         <v>93</v>
@@ -3709,7 +3709,7 @@
         <v>4321</v>
       </c>
       <c r="P47" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q47" s="8" t="s">
         <v>105</v>
@@ -3748,7 +3748,7 @@
         <v>1234</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J48" s="7" t="s">
         <v>93</v>
@@ -3769,7 +3769,7 @@
         <v>4321</v>
       </c>
       <c r="P48" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q48" s="8" t="s">
         <v>105</v>
@@ -3808,7 +3808,7 @@
         <v>1234</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J49" s="7" t="s">
         <v>93</v>
@@ -3829,7 +3829,7 @@
         <v>4321</v>
       </c>
       <c r="P49" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q49" s="8" t="s">
         <v>105</v>
@@ -3868,7 +3868,7 @@
         <v>1234</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J50" s="11" t="s">
         <v>106</v>
@@ -3889,7 +3889,7 @@
         <v>4321</v>
       </c>
       <c r="P50" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q50" s="8" t="s">
         <v>105</v>
@@ -3928,7 +3928,7 @@
         <v>1234</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J51" s="11" t="s">
         <v>106</v>
@@ -3949,7 +3949,7 @@
         <v>4321</v>
       </c>
       <c r="P51" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q51" s="8" t="s">
         <v>105</v>
@@ -3988,7 +3988,7 @@
         <v>1234</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J52" s="11" t="s">
         <v>106</v>
@@ -4009,7 +4009,7 @@
         <v>4321</v>
       </c>
       <c r="P52" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q52" s="8" t="s">
         <v>105</v>
@@ -4048,7 +4048,7 @@
         <v>1234</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J53" s="11" t="s">
         <v>106</v>
@@ -4069,7 +4069,7 @@
         <v>4321</v>
       </c>
       <c r="P53" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q53" s="8" t="s">
         <v>105</v>
@@ -4108,7 +4108,7 @@
         <v>1234</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J54" s="11" t="s">
         <v>106</v>
@@ -4129,7 +4129,7 @@
         <v>4321</v>
       </c>
       <c r="P54" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q54" s="8" t="s">
         <v>105</v>
@@ -4168,7 +4168,7 @@
         <v>1234</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J55" s="11" t="s">
         <v>106</v>
@@ -4189,7 +4189,7 @@
         <v>4321</v>
       </c>
       <c r="P55" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q55" s="8" t="s">
         <v>105</v>
@@ -4228,7 +4228,7 @@
         <v>1234</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J56" s="8" t="s">
         <v>105</v>
@@ -4249,7 +4249,7 @@
         <v>4321</v>
       </c>
       <c r="P56" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q56" s="7" t="s">
         <v>93</v>
@@ -4288,7 +4288,7 @@
         <v>1234</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J57" s="8" t="s">
         <v>105</v>
@@ -4309,7 +4309,7 @@
         <v>4321</v>
       </c>
       <c r="P57" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q57" s="7" t="s">
         <v>93</v>
@@ -4348,7 +4348,7 @@
         <v>1234</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J58" s="8" t="s">
         <v>105</v>
@@ -4369,7 +4369,7 @@
         <v>4321</v>
       </c>
       <c r="P58" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q58" s="7" t="s">
         <v>93</v>
@@ -4408,7 +4408,7 @@
         <v>1234</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J59" s="8" t="s">
         <v>105</v>
@@ -4429,7 +4429,7 @@
         <v>4321</v>
       </c>
       <c r="P59" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q59" s="7" t="s">
         <v>93</v>
@@ -4468,7 +4468,7 @@
         <v>1234</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J60" s="8" t="s">
         <v>105</v>
@@ -4489,7 +4489,7 @@
         <v>4321</v>
       </c>
       <c r="P60" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q60" s="7" t="s">
         <v>93</v>
@@ -4528,7 +4528,7 @@
         <v>1234</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J61" s="8" t="s">
         <v>105</v>
@@ -4549,7 +4549,7 @@
         <v>4321</v>
       </c>
       <c r="P61" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q61" s="7" t="s">
         <v>93</v>
@@ -4588,7 +4588,7 @@
         <v>1234</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J62" s="9" t="s">
         <v>107</v>
@@ -4609,7 +4609,7 @@
         <v>4321</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q62" s="9" t="s">
         <v>95</v>
@@ -4648,7 +4648,7 @@
         <v>1234</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J63" s="9" t="s">
         <v>107</v>
@@ -4669,7 +4669,7 @@
         <v>4321</v>
       </c>
       <c r="P63" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q63" s="9" t="s">
         <v>95</v>
@@ -4708,7 +4708,7 @@
         <v>1234</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J64" s="9" t="s">
         <v>107</v>
@@ -4729,7 +4729,7 @@
         <v>4321</v>
       </c>
       <c r="P64" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q64" s="9" t="s">
         <v>95</v>
@@ -4768,7 +4768,7 @@
         <v>1234</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J65" s="9" t="s">
         <v>107</v>
@@ -4789,7 +4789,7 @@
         <v>4321</v>
       </c>
       <c r="P65" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q65" s="9" t="s">
         <v>95</v>
@@ -4828,7 +4828,7 @@
         <v>1234</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J66" s="9" t="s">
         <v>107</v>
@@ -4849,7 +4849,7 @@
         <v>4321</v>
       </c>
       <c r="P66" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q66" s="9" t="s">
         <v>95</v>
@@ -4888,7 +4888,7 @@
         <v>1234</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J67" s="9" t="s">
         <v>107</v>
@@ -4909,7 +4909,7 @@
         <v>4321</v>
       </c>
       <c r="P67" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q67" s="9" t="s">
         <v>95</v>
@@ -4948,7 +4948,7 @@
         <v>1234</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J68" s="9" t="s">
         <v>107</v>
@@ -4969,7 +4969,7 @@
         <v>4321</v>
       </c>
       <c r="P68" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q68" s="7" t="s">
         <v>93</v>
@@ -5008,7 +5008,7 @@
         <v>1234</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J69" s="9" t="s">
         <v>107</v>
@@ -5029,7 +5029,7 @@
         <v>4321</v>
       </c>
       <c r="P69" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q69" s="7" t="s">
         <v>93</v>
@@ -5068,7 +5068,7 @@
         <v>1234</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J70" s="9" t="s">
         <v>107</v>
@@ -5089,7 +5089,7 @@
         <v>4321</v>
       </c>
       <c r="P70" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q70" s="7" t="s">
         <v>93</v>
@@ -5128,7 +5128,7 @@
         <v>1234</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J71" s="9" t="s">
         <v>107</v>
@@ -5149,7 +5149,7 @@
         <v>4321</v>
       </c>
       <c r="P71" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q71" s="7" t="s">
         <v>93</v>
@@ -5188,7 +5188,7 @@
         <v>1234</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J72" s="9" t="s">
         <v>107</v>
@@ -5209,7 +5209,7 @@
         <v>4321</v>
       </c>
       <c r="P72" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q72" s="7" t="s">
         <v>93</v>
@@ -5248,7 +5248,7 @@
         <v>1234</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J73" s="9" t="s">
         <v>107</v>
@@ -5269,7 +5269,7 @@
         <v>4321</v>
       </c>
       <c r="P73" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q73" s="7" t="s">
         <v>93</v>
@@ -5308,7 +5308,7 @@
         <v>1234</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J74" s="8" t="s">
         <v>105</v>
@@ -5329,7 +5329,7 @@
         <v>4321</v>
       </c>
       <c r="P74" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q74" s="9" t="s">
         <v>95</v>
@@ -5368,7 +5368,7 @@
         <v>1234</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J75" s="8" t="s">
         <v>105</v>
@@ -5389,7 +5389,7 @@
         <v>4321</v>
       </c>
       <c r="P75" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q75" s="9" t="s">
         <v>95</v>
@@ -5428,7 +5428,7 @@
         <v>1234</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J76" s="8" t="s">
         <v>105</v>
@@ -5449,7 +5449,7 @@
         <v>4321</v>
       </c>
       <c r="P76" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q76" s="9" t="s">
         <v>95</v>
@@ -5488,7 +5488,7 @@
         <v>1234</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J77" s="8" t="s">
         <v>105</v>
@@ -5509,7 +5509,7 @@
         <v>4321</v>
       </c>
       <c r="P77" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q77" s="9" t="s">
         <v>95</v>
@@ -5548,7 +5548,7 @@
         <v>1234</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J78" s="8" t="s">
         <v>105</v>
@@ -5569,7 +5569,7 @@
         <v>4321</v>
       </c>
       <c r="P78" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q78" s="9" t="s">
         <v>95</v>
@@ -5608,7 +5608,7 @@
         <v>1234</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J79" s="8" t="s">
         <v>105</v>
@@ -5629,7 +5629,7 @@
         <v>4321</v>
       </c>
       <c r="P79" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q79" s="9" t="s">
         <v>95</v>
@@ -5668,7 +5668,7 @@
         <v>1234</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J80" s="7" t="s">
         <v>93</v>
@@ -5689,7 +5689,7 @@
         <v>4321</v>
       </c>
       <c r="P80" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q80" s="7" t="s">
         <v>93</v>
@@ -5728,7 +5728,7 @@
         <v>1234</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J81" s="7" t="s">
         <v>93</v>
@@ -5749,7 +5749,7 @@
         <v>4321</v>
       </c>
       <c r="P81" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q81" s="7" t="s">
         <v>93</v>
@@ -5788,7 +5788,7 @@
         <v>1234</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J82" s="7" t="s">
         <v>93</v>
@@ -5809,7 +5809,7 @@
         <v>4321</v>
       </c>
       <c r="P82" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q82" s="7" t="s">
         <v>93</v>
@@ -5848,7 +5848,7 @@
         <v>1234</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J83" s="7" t="s">
         <v>93</v>
@@ -5869,7 +5869,7 @@
         <v>4321</v>
       </c>
       <c r="P83" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q83" s="7" t="s">
         <v>93</v>
@@ -5908,7 +5908,7 @@
         <v>1234</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J84" s="7" t="s">
         <v>93</v>
@@ -5929,7 +5929,7 @@
         <v>4321</v>
       </c>
       <c r="P84" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q84" s="7" t="s">
         <v>93</v>
@@ -5968,7 +5968,7 @@
         <v>1234</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J85" s="7" t="s">
         <v>93</v>
@@ -5989,7 +5989,7 @@
         <v>4321</v>
       </c>
       <c r="P85" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q85" s="7" t="s">
         <v>93</v>
@@ -6028,7 +6028,7 @@
         <v>1234</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J86" s="7" t="s">
         <v>93</v>
@@ -6049,7 +6049,7 @@
         <v>4321</v>
       </c>
       <c r="P86" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q86" s="7" t="s">
         <v>93</v>
@@ -6088,7 +6088,7 @@
         <v>1234</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J87" s="7" t="s">
         <v>93</v>
@@ -6109,7 +6109,7 @@
         <v>4321</v>
       </c>
       <c r="P87" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q87" s="7" t="s">
         <v>93</v>
@@ -6148,7 +6148,7 @@
         <v>1234</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J88" s="7" t="s">
         <v>93</v>
@@ -6169,7 +6169,7 @@
         <v>4321</v>
       </c>
       <c r="P88" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q88" s="7" t="s">
         <v>93</v>
@@ -6208,7 +6208,7 @@
         <v>1234</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J89" s="7" t="s">
         <v>93</v>
@@ -6229,7 +6229,7 @@
         <v>4321</v>
       </c>
       <c r="P89" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q89" s="7" t="s">
         <v>93</v>
@@ -6268,7 +6268,7 @@
         <v>1234</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J90" s="7" t="s">
         <v>93</v>
@@ -6289,7 +6289,7 @@
         <v>4321</v>
       </c>
       <c r="P90" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q90" s="7" t="s">
         <v>93</v>
@@ -6328,7 +6328,7 @@
         <v>1234</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J91" s="7" t="s">
         <v>93</v>
@@ -6349,7 +6349,7 @@
         <v>4321</v>
       </c>
       <c r="P91" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="Q91" s="7" t="s">
         <v>93</v>
